--- a/source/NebulaCost.xlsx
+++ b/source/NebulaCost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1337c\OneDrive\Skrivbord\Projects\Nebula calc\source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1337c\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BBDD93-20FA-4D48-A92C-DBC32136292D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168C46B6-0C27-4136-BE4F-0D2C21F5EECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{862659F1-DB39-499A-B41E-83BAA2ACBE5C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{862659F1-DB39-499A-B41E-83BAA2ACBE5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Nebula cost" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="105">
   <si>
     <t>Shard</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Ingot</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
     <t>300 000</t>
   </si>
   <si>
@@ -200,27 +197,6 @@
     <t>Tier 6</t>
   </si>
   <si>
-    <t>7 500 000</t>
-  </si>
-  <si>
-    <t>7 700 000</t>
-  </si>
-  <si>
-    <t>7 900 000</t>
-  </si>
-  <si>
-    <t>8 100 000</t>
-  </si>
-  <si>
-    <t>8 300 000</t>
-  </si>
-  <si>
-    <t>8 500 000</t>
-  </si>
-  <si>
-    <t>48 000 000</t>
-  </si>
-  <si>
     <t>Tier 7</t>
   </si>
   <si>
@@ -372,6 +348,12 @@
   </si>
   <si>
     <t>7-7</t>
+  </si>
+  <si>
+    <t>Tier 0</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -447,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -474,6 +456,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -810,14 +801,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{042D68B2-A70B-4E63-990F-FD8840843BD5}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="11.54296875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="12.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="11.1796875" customWidth="1"/>
     <col min="11" max="11" width="13.1796875" customWidth="1"/>
@@ -844,7 +835,7 @@
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -856,11 +847,11 @@
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="6" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>6</v>
@@ -880,7 +871,7 @@
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3">
         <v>50</v>
@@ -888,11 +879,11 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="7" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -901,43 +892,51 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="3">
-        <v>100</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2">
+        <f>B3</f>
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f>E3</f>
+        <v>300 000</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="3">
-        <v>150</v>
-      </c>
+      <c r="A5" s="10"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="7" t="s">
-        <v>63</v>
-      </c>
+      <c r="G5" s="10"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -945,42 +944,56 @@
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="3">
-        <v>200</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+      <c r="A6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -990,19 +1003,19 @@
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1012,19 +1025,19 @@
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1034,72 +1047,64 @@
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="B10" s="3">
+        <v>250</v>
+      </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3">
-        <v>500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>20</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1350</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>500</v>
-      </c>
-      <c r="J11" s="2">
-        <v>20</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
+      <c r="A11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3">
+        <v>300</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="3">
+        <v>350</v>
+      </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1107,79 +1112,74 @@
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>500</v>
+      </c>
+      <c r="J13" s="3">
+        <v>20</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="3">
-        <v>450</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1350</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <f>500000+700000+900000+1100000+1300000+1500000</f>
+        <v>6000000</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>500</v>
+      </c>
+      <c r="J14" s="2">
+        <v>20</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="3">
-        <v>500</v>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="7" t="s">
-        <v>70</v>
-      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1187,42 +1187,56 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="3">
-        <v>550</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B17" s="3">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1232,19 +1246,19 @@
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B18" s="3">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1254,19 +1268,19 @@
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="7" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1276,68 +1290,64 @@
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="4"/>
+        <v>64</v>
+      </c>
+      <c r="B20" s="3">
+        <v>600</v>
+      </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2</v>
-      </c>
-      <c r="I20" s="3">
-        <v>800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>30</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="2">
-        <v>3450</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="2">
-        <v>2</v>
-      </c>
-      <c r="I21" s="2">
-        <v>800</v>
-      </c>
-      <c r="J21" s="2">
-        <v>30</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
+      <c r="A21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="3">
+        <v>650</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3">
+        <v>700</v>
+      </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="8"/>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1345,83 +1355,69 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2</v>
+      </c>
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>30</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3450</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2">
         <v>800</v>
       </c>
-      <c r="C24" s="3">
-        <v>100</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="J24" s="2">
+        <v>30</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="3">
-        <v>850</v>
-      </c>
-      <c r="C25" s="3">
-        <v>150</v>
-      </c>
+      <c r="A25" s="8"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="7" t="s">
-        <v>77</v>
-      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="8"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1429,46 +1425,58 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="3">
-        <v>900</v>
-      </c>
-      <c r="C26" s="3">
-        <v>200</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="A26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B27" s="3">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="C27" s="3">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1478,21 +1486,21 @@
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="C28" s="3">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="7" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1502,21 +1510,21 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="C29" s="3">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1526,72 +1534,70 @@
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="B30" s="3">
+        <v>950</v>
+      </c>
+      <c r="C30" s="3">
+        <v>250</v>
+      </c>
       <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="E30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="3">
-        <v>3</v>
-      </c>
-      <c r="I30" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J30" s="3">
-        <v>40</v>
-      </c>
-      <c r="K30" s="3">
-        <v>20</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="2">
-        <v>5550</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1350</v>
-      </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="2">
-        <v>3</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J31" s="2">
-        <v>40</v>
-      </c>
-      <c r="K31" s="2">
-        <v>20</v>
-      </c>
-      <c r="L31" s="2">
-        <v>0</v>
-      </c>
+      <c r="A31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C31" s="3">
+        <v>300</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
     </row>
     <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="A32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1050</v>
+      </c>
+      <c r="C32" s="3">
+        <v>350</v>
+      </c>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="8"/>
+      <c r="E32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1599,83 +1605,73 @@
       <c r="L32" s="4"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J33" s="2" t="s">
+      <c r="I33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>40</v>
+      </c>
+      <c r="K33" s="3">
+        <v>20</v>
+      </c>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="2">
+        <v>5550</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1350</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2">
         <v>3</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="3">
-        <v>1150</v>
-      </c>
-      <c r="C34" s="3">
-        <v>450</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
+      <c r="I34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="2">
+        <v>40</v>
+      </c>
+      <c r="K34" s="2">
+        <v>20</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="C35" s="3">
-        <v>500</v>
-      </c>
+      <c r="A35" s="8"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="8"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -1683,46 +1679,58 @@
       <c r="L35" s="4"/>
     </row>
     <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="3">
-        <v>1250</v>
-      </c>
-      <c r="C36" s="3">
-        <v>550</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="A36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="7" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B37" s="3">
-        <v>1300</v>
+        <v>1150</v>
       </c>
       <c r="C37" s="3">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="7" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -1732,21 +1740,21 @@
     </row>
     <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="7" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B38" s="3">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="C38" s="3">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="7" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -1756,21 +1764,21 @@
     </row>
     <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="C39" s="3">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -1780,72 +1788,70 @@
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1300</v>
+      </c>
+      <c r="C40" s="3">
+        <v>600</v>
+      </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="E40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H40" s="3">
-        <v>5</v>
-      </c>
-      <c r="I40" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J40" s="3">
-        <v>50</v>
-      </c>
-      <c r="K40" s="3">
-        <v>30</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="2">
-        <v>7650</v>
-      </c>
-      <c r="C41" s="2">
-        <v>3450</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="2">
-        <v>5</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41" s="2">
-        <v>50</v>
-      </c>
-      <c r="K41" s="2">
-        <v>30</v>
-      </c>
-      <c r="L41" s="2">
-        <v>0</v>
-      </c>
+      <c r="A41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1350</v>
+      </c>
+      <c r="C41" s="3">
+        <v>650</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="8"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="A42" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="C42" s="3">
+        <v>700</v>
+      </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="8"/>
+      <c r="E42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1853,83 +1859,73 @@
       <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="A43" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H43" s="3">
         <v>5</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="2" t="s">
+      <c r="I43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>50</v>
+      </c>
+      <c r="K43" s="3">
+        <v>30</v>
+      </c>
+      <c r="L43" s="4"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="2">
+        <v>7650</v>
+      </c>
+      <c r="C44" s="2">
+        <v>3450</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="3">
-        <v>800</v>
-      </c>
-      <c r="D44" s="3">
-        <v>100</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
+      <c r="I44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="2">
+        <v>50</v>
+      </c>
+      <c r="K44" s="2">
+        <v>30</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="A45" s="8"/>
       <c r="B45" s="4"/>
-      <c r="C45" s="3">
-        <v>850</v>
-      </c>
-      <c r="D45" s="3">
-        <v>150</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="8"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -1937,46 +1933,58 @@
       <c r="L45" s="4"/>
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="3">
-        <v>900</v>
-      </c>
-      <c r="D46" s="3">
-        <v>200</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
+      <c r="A46" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="3">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="D47" s="3">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -1986,21 +1994,21 @@
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="3">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -2010,21 +2018,21 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="3">
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="D49" s="3">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -2034,72 +2042,70 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="C50" s="3">
+        <v>950</v>
+      </c>
+      <c r="D50" s="3">
+        <v>250</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="H50" s="3">
-        <v>7</v>
-      </c>
-      <c r="I50" s="3">
-        <v>3000</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-      <c r="K50" s="3">
-        <v>40</v>
-      </c>
-      <c r="L50" s="3">
-        <v>20</v>
-      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="2">
-        <v>0</v>
-      </c>
-      <c r="C51" s="2">
-        <v>5550</v>
-      </c>
-      <c r="D51" s="1"/>
-      <c r="E51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H51" s="2">
-        <v>7</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J51" s="2">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2">
-        <v>40</v>
-      </c>
-      <c r="L51" s="2">
-        <v>20</v>
-      </c>
+      <c r="A51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D51" s="3">
+        <v>300</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="8"/>
+      <c r="A52" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="8"/>
+      <c r="C52" s="3">
+        <v>1050</v>
+      </c>
+      <c r="D52" s="3">
+        <v>350</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2107,83 +2113,73 @@
       <c r="L52" s="4"/>
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I53" s="2" t="s">
+      <c r="A53" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" s="3">
         <v>7</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>5</v>
+      <c r="I53" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="3">
+        <v>40</v>
+      </c>
+      <c r="L53" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="3">
-        <v>1150</v>
-      </c>
-      <c r="D54" s="3">
-        <v>450</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
+      <c r="A54" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2">
+        <v>5550</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2">
+        <v>7</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2">
+        <v>40</v>
+      </c>
+      <c r="L54" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="A55" s="8"/>
       <c r="B55" s="4"/>
-      <c r="C55" s="3">
-        <v>1200</v>
-      </c>
-      <c r="D55" s="3">
-        <v>500</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="8"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -2191,46 +2187,58 @@
       <c r="L55" s="4"/>
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="3">
-        <v>1250</v>
-      </c>
-      <c r="D56" s="3">
-        <v>550</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
+      <c r="A56" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="7" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="3">
-        <v>1300</v>
+        <v>1150</v>
       </c>
       <c r="D57" s="3">
-        <v>600</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>56</v>
+        <v>450</v>
+      </c>
+      <c r="E57" s="11">
+        <v>7500000</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="7" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -2240,21 +2248,21 @@
     </row>
     <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="7" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="3">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="D58" s="3">
-        <v>650</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>57</v>
+        <v>500</v>
+      </c>
+      <c r="E58" s="11">
+        <v>7700000</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="7" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -2264,21 +2272,21 @@
     </row>
     <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="3">
-        <v>1400</v>
+        <v>1250</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>58</v>
+        <v>550</v>
+      </c>
+      <c r="E59" s="11">
+        <v>7900000</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -2288,70 +2296,70 @@
     </row>
     <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="7" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="C60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="11">
+        <v>8100000</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H60" s="3">
-        <v>10</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
-      <c r="K60" s="3">
-        <v>50</v>
-      </c>
-      <c r="L60" s="3">
-        <v>30</v>
-      </c>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
     </row>
     <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B61" s="2">
-        <v>0</v>
-      </c>
-      <c r="C61" s="2">
-        <v>7650</v>
-      </c>
-      <c r="D61" s="1"/>
-      <c r="E61" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="2">
-        <v>10</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>0</v>
-      </c>
-      <c r="K61" s="2">
-        <v>50</v>
-      </c>
-      <c r="L61" s="2">
-        <v>30</v>
-      </c>
+      <c r="A61" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="3">
+        <v>1350</v>
+      </c>
+      <c r="D61" s="3">
+        <v>650</v>
+      </c>
+      <c r="E61" s="11">
+        <v>8300000</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
     </row>
     <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="8"/>
+      <c r="A62" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="8"/>
+      <c r="C62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="11">
+        <v>8500000</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
@@ -2359,83 +2367,72 @@
       <c r="L62" s="4"/>
     </row>
     <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>5</v>
+      <c r="A63" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H63" s="3">
+        <v>10</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="3">
+        <v>50</v>
+      </c>
+      <c r="L63" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="3">
-        <v>1500</v>
-      </c>
-      <c r="D64" s="3">
-        <v>800</v>
-      </c>
-      <c r="E64" s="3">
-        <v>8900000</v>
-      </c>
-      <c r="F64" s="4"/>
-      <c r="G64" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
+      <c r="A64" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0</v>
+      </c>
+      <c r="C64" s="2">
+        <v>7650</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="12">
+        <f>SUM(E57:E62)</f>
+        <v>48000000</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2">
+        <v>10</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2">
+        <v>50</v>
+      </c>
+      <c r="L64" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="A65" s="8"/>
       <c r="B65" s="4"/>
-      <c r="C65" s="3">
-        <v>1550</v>
-      </c>
-      <c r="D65" s="3">
-        <v>850</v>
-      </c>
-      <c r="E65" s="3">
-        <v>9100000</v>
-      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-      <c r="G65" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="G65" s="8"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
@@ -2443,46 +2440,58 @@
       <c r="L65" s="4"/>
     </row>
     <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="3">
-        <v>1600</v>
-      </c>
-      <c r="D66" s="3">
-        <v>900</v>
-      </c>
-      <c r="E66" s="3">
-        <v>9300000</v>
-      </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
+      <c r="A66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" s="9"/>
+      <c r="G66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="3">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="3">
-        <v>950</v>
-      </c>
-      <c r="E67" s="3">
-        <v>9500000</v>
+        <v>800</v>
+      </c>
+      <c r="E67" s="11">
+        <v>8900000</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -2492,21 +2501,21 @@
     </row>
     <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="3">
-        <v>1700</v>
+        <v>1550</v>
       </c>
       <c r="D68" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E68" s="3">
-        <v>9700000</v>
+        <v>850</v>
+      </c>
+      <c r="E68" s="11">
+        <v>9100000</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="7" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -2516,21 +2525,21 @@
     </row>
     <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="3">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="D69" s="3">
-        <v>1050</v>
-      </c>
-      <c r="E69" s="3">
-        <v>9900000</v>
+        <v>900</v>
+      </c>
+      <c r="E69" s="11">
+        <v>9300000</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -2540,59 +2549,132 @@
     </row>
     <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="7" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
+      <c r="C70" s="3">
+        <v>1650</v>
+      </c>
+      <c r="D70" s="3">
+        <v>950</v>
+      </c>
+      <c r="E70" s="11">
+        <v>9500000</v>
+      </c>
       <c r="F70" s="4"/>
       <c r="G70" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H70" s="4">
-        <v>0</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
-      <c r="K70" s="4">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4">
-        <v>0</v>
-      </c>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
     </row>
     <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B71" s="2">
-        <v>0</v>
-      </c>
-      <c r="C71" s="2">
-        <v>0</v>
-      </c>
-      <c r="D71" s="1"/>
-      <c r="E71" s="2">
-        <v>0</v>
-      </c>
-      <c r="F71" s="9"/>
-      <c r="G71" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H71" s="2">
-        <v>0</v>
-      </c>
-      <c r="I71" s="2">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
-        <v>0</v>
-      </c>
-      <c r="K71" s="2">
-        <v>0</v>
-      </c>
-      <c r="L71" s="2">
+      <c r="A71" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="3">
+        <v>1700</v>
+      </c>
+      <c r="D71" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E71" s="11">
+        <v>9700000</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+    </row>
+    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="3">
+        <v>1750</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1050</v>
+      </c>
+      <c r="E72" s="11">
+        <v>9900000</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H73" s="4">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="12">
+        <f>SUM(E67:E72)</f>
+        <v>56400000</v>
+      </c>
+      <c r="F74" s="9"/>
+      <c r="G74" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2">
         <v>0</v>
       </c>
     </row>
